--- a/tiflow-diga/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Communication-DiGA.xlsx
+++ b/tiflow-diga/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Communication-DiGA.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="363">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -442,6 +442,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -484,10 +494,17 @@
     <t>Allows identification of the communication as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Event.identifier</t>
   </si>
   <si>
     <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>Communication.instantiatesCanonical</t>
@@ -503,6 +520,9 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -544,7 +564,14 @@
     <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Communication.basedOn.id</t>
@@ -570,16 +597,6 @@
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -676,6 +693,9 @@
     <t>Part of this action.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -754,6 +774,9 @@
     <t>Event.statusReason</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -806,6 +829,9 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1119,7 +1145,13 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
+  </si>
+  <si>
     <t>Event.note</t>
+  </si>
+  <si>
+    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1480,7 +1512,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2450,19 +2482,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2474,7 +2506,7 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2488,10 +2520,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2517,16 +2549,16 @@
         <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>136</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2563,19 +2595,19 @@
         <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2587,7 +2619,7 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2601,10 +2633,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2627,19 +2659,19 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2688,7 +2720,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2697,27 +2729,27 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2740,15 +2772,17 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2797,7 +2831,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2812,21 +2846,21 @@
         <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2852,13 +2886,13 @@
         <v>101</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2908,7 +2942,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2923,25 +2957,25 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2960,16 +2994,16 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3019,7 +3053,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3028,27 +3062,27 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3071,13 +3105,13 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3128,7 +3162,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3149,15 +3183,15 @@
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3186,7 +3220,7 @@
         <v>134</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>136</v>
@@ -3227,19 +3261,19 @@
         <v>77</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3251,7 +3285,7 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
@@ -3260,15 +3294,15 @@
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3291,16 +3325,16 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3350,7 +3384,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3359,7 +3393,7 @@
         <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>99</v>
@@ -3376,10 +3410,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3405,13 +3439,13 @@
         <v>101</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3437,13 +3471,13 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>77</v>
@@ -3461,7 +3495,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3487,10 +3521,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3513,16 +3547,16 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3572,7 +3606,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3581,7 +3615,7 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>99</v>
@@ -3593,15 +3627,15 @@
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3624,16 +3658,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3683,7 +3717,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3709,14 +3743,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3735,15 +3769,17 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -3792,7 +3828,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3801,27 +3837,27 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3844,15 +3880,17 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3901,7 +3939,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3910,10 +3948,10 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
@@ -3922,15 +3960,15 @@
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3956,13 +3994,13 @@
         <v>107</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3970,7 +4008,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>77</v>
@@ -3988,31 +4026,31 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>87</v>
@@ -4027,10 +4065,10 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4038,14 +4076,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4064,16 +4102,16 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4099,31 +4137,31 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4132,27 +4170,27 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>77</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4175,16 +4213,16 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4210,13 +4248,13 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4234,7 +4272,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4243,7 +4281,7 @@
         <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>99</v>
@@ -4252,18 +4290,18 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4289,20 +4327,20 @@
         <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q26" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="R26" t="s" s="2">
         <v>77</v>
@@ -4323,13 +4361,13 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4347,7 +4385,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4365,7 +4403,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4373,10 +4411,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4399,15 +4437,17 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4432,13 +4472,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4456,7 +4496,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4465,7 +4505,7 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>99</v>
@@ -4477,19 +4517,19 @@
         <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>77</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4508,15 +4548,17 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4565,7 +4607,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4574,27 +4616,27 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4617,16 +4659,16 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4652,13 +4694,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -4676,7 +4718,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4685,7 +4727,7 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
@@ -4694,18 +4736,18 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>77</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4728,16 +4770,16 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4787,7 +4829,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4796,27 +4838,27 @@
         <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4839,16 +4881,16 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4898,7 +4940,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4907,27 +4949,27 @@
         <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4950,16 +4992,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5009,7 +5051,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5024,10 +5066,10 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5035,10 +5077,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5061,16 +5103,16 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5120,7 +5162,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5135,10 +5177,10 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5146,10 +5188,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5172,16 +5214,16 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5231,7 +5273,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5240,27 +5282,27 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5283,13 +5325,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5340,7 +5382,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5361,15 +5403,15 @@
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5398,7 +5440,7 @@
         <v>134</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>136</v>
@@ -5439,19 +5481,19 @@
         <v>77</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5463,7 +5505,7 @@
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
@@ -5472,15 +5514,15 @@
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5503,16 +5545,16 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5562,7 +5604,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5571,7 +5613,7 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>99</v>
@@ -5588,10 +5630,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5617,13 +5659,13 @@
         <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5649,13 +5691,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -5673,7 +5715,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5699,10 +5741,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5725,16 +5767,16 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5784,7 +5826,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5793,7 +5835,7 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>99</v>
@@ -5805,15 +5847,15 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5836,16 +5878,16 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5895,7 +5937,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5921,10 +5963,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5947,16 +5989,16 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6006,7 +6048,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6015,27 +6057,27 @@
         <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6058,13 +6100,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6115,7 +6157,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6136,15 +6178,15 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6173,7 +6215,7 @@
         <v>134</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>136</v>
@@ -6214,19 +6256,19 @@
         <v>77</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6238,7 +6280,7 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6247,15 +6289,15 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6278,16 +6320,16 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6337,7 +6379,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6346,7 +6388,7 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>99</v>
@@ -6363,10 +6405,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6392,13 +6434,13 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6424,13 +6466,13 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -6448,7 +6490,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6474,10 +6516,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6500,16 +6542,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6559,7 +6601,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6568,7 +6610,7 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>99</v>
@@ -6580,15 +6622,15 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6611,16 +6653,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6670,7 +6712,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6696,10 +6738,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6722,16 +6764,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6757,13 +6799,13 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -6781,7 +6823,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6790,27 +6832,27 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6833,15 +6875,17 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -6890,7 +6934,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -6899,27 +6943,27 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6942,13 +6986,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6999,7 +7043,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7008,7 +7052,7 @@
         <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>99</v>
@@ -7020,15 +7064,15 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7051,13 +7095,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7108,7 +7152,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7129,15 +7173,15 @@
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7166,7 +7210,7 @@
         <v>134</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>136</v>
@@ -7207,19 +7251,19 @@
         <v>77</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7231,7 +7275,7 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7240,19 +7284,19 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7274,16 +7318,16 @@
         <v>133</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>136</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7332,7 +7376,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7344,7 +7388,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7358,10 +7402,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7384,16 +7428,16 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7443,7 +7487,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>87</v>
@@ -7452,7 +7496,7 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>99</v>
@@ -7464,15 +7508,15 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7495,15 +7539,17 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7552,7 +7598,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7561,19 +7607,19 @@
         <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>77</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
